--- a/list.xlsx
+++ b/list.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Randomizer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\projects\github.com\Demparty\an.mn\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8DA764D-6DE5-40DB-B3D3-050B98070A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="list" sheetId="1" r:id="rId1"/>
@@ -19,38 +20,51 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>total_pool</t>
   </si>
   <si>
     <t>choose_pool</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>uuriin_hayg</t>
+  </si>
+  <si>
+    <t>test 1</t>
+  </si>
+  <si>
+    <t>test 2</t>
+  </si>
+  <si>
+    <t>test 3</t>
+  </si>
+  <si>
+    <t>test 4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -411,51 +425,82 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="10.9375" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
         <v>15</v>
       </c>
-      <c r="B2">
+      <c r="D2">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3">
         <v>20</v>
       </c>
-      <c r="B3">
+      <c r="D3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
         <v>13</v>
       </c>
-      <c r="B4">
+      <c r="D4">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
         <v>35</v>
       </c>
-      <c r="B5">
+      <c r="D5">
         <v>8</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/list.xlsx
+++ b/list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\projects\github.com\Demparty\an.mn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8DA764D-6DE5-40DB-B3D3-050B98070A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9561DDAB-9C28-4AD9-8BA1-FC17D7639418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,22 +33,22 @@
     <t>choose_pool</t>
   </si>
   <si>
+    <t>uuriin_hayg</t>
+  </si>
+  <si>
+    <t>test 1</t>
+  </si>
+  <si>
+    <t>test 2</t>
+  </si>
+  <si>
+    <t>test 3</t>
+  </si>
+  <si>
+    <t>test 4</t>
+  </si>
+  <si>
     <t>id</t>
-  </si>
-  <si>
-    <t>uuriin_hayg</t>
-  </si>
-  <si>
-    <t>test 1</t>
-  </si>
-  <si>
-    <t>test 2</t>
-  </si>
-  <si>
-    <t>test 3</t>
-  </si>
-  <si>
-    <t>test 4</t>
   </si>
 </sst>
 </file>
@@ -431,10 +431,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -448,7 +448,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>15</v>
@@ -462,7 +462,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -476,7 +476,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>13</v>
@@ -490,7 +490,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>35</v>

--- a/list.xlsx
+++ b/list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\projects\github.com\Demparty\an.mn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9561DDAB-9C28-4AD9-8BA1-FC17D7639418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1593CB-B372-4199-9607-87A36F63F68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,9 +33,6 @@
     <t>choose_pool</t>
   </si>
   <si>
-    <t>uuriin_hayg</t>
-  </si>
-  <si>
     <t>test 1</t>
   </si>
   <si>
@@ -49,6 +46,9 @@
   </si>
   <si>
     <t>id</t>
+  </si>
+  <si>
+    <t>sector_name</t>
   </si>
 </sst>
 </file>
@@ -431,10 +431,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
         <v>7</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -448,7 +448,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>15</v>
@@ -462,7 +462,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -476,7 +476,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>13</v>
@@ -490,7 +490,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>35</v>

--- a/list.xlsx
+++ b/list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\projects\github.com\Demparty\an.mn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1593CB-B372-4199-9607-87A36F63F68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5ACE5BE-C170-4492-B05E-AE54F0FB70E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,13 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>total_pool</t>
-  </si>
-  <si>
-    <t>choose_pool</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>test 1</t>
   </si>
@@ -49,6 +43,24 @@
   </si>
   <si>
     <t>sector_name</t>
+  </si>
+  <si>
+    <t>file_name</t>
+  </si>
+  <si>
+    <t>list1.xlsx</t>
+  </si>
+  <si>
+    <t>list2.xlsx</t>
+  </si>
+  <si>
+    <t>list3.xlsx</t>
+  </si>
+  <si>
+    <t>list4.xlsx</t>
+  </si>
+  <si>
+    <t>choose_count</t>
   </si>
 </sst>
 </file>
@@ -428,19 +440,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="10.9375" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="1" max="1" width="4.6875" customWidth="1"/>
+    <col min="2" max="2" width="12.9375" customWidth="1"/>
+    <col min="4" max="4" width="12.875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.5">
@@ -448,13 +465,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>15</v>
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.5">
@@ -462,13 +479,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>20</v>
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.5">
@@ -476,13 +493,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.5">
@@ -490,13 +507,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>35</v>
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/list.xlsx
+++ b/list.xlsx
@@ -1,43 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\projects\github.com\Demparty\an.mn\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/murun/Downloads/an.mn-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5ACE5BE-C170-4492-B05E-AE54F0FB70E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF8F680-6F3D-9946-9BC0-BCD2FAD5C6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34400" yWindow="600" windowWidth="34400" windowHeight="26980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="list" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>test 1</t>
-  </si>
-  <si>
-    <t>test 2</t>
-  </si>
-  <si>
-    <t>test 3</t>
-  </si>
-  <si>
-    <t>test 4</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="374">
   <si>
     <t>id</t>
   </si>
@@ -48,19 +47,1117 @@
     <t>file_name</t>
   </si>
   <si>
-    <t>list1.xlsx</t>
-  </si>
-  <si>
-    <t>list2.xlsx</t>
-  </si>
-  <si>
-    <t>list3.xlsx</t>
-  </si>
-  <si>
-    <t>list4.xlsx</t>
-  </si>
-  <si>
     <t>choose_count</t>
+  </si>
+  <si>
+    <t>BGD01</t>
+  </si>
+  <si>
+    <t>BGD02</t>
+  </si>
+  <si>
+    <t>BGD04</t>
+  </si>
+  <si>
+    <t>BGD05</t>
+  </si>
+  <si>
+    <t>BGD06</t>
+  </si>
+  <si>
+    <t>BGD08</t>
+  </si>
+  <si>
+    <t>BGD09</t>
+  </si>
+  <si>
+    <t>BGD10</t>
+  </si>
+  <si>
+    <t>BGD11</t>
+  </si>
+  <si>
+    <t>BGD12</t>
+  </si>
+  <si>
+    <t>BGD15</t>
+  </si>
+  <si>
+    <t>BGD16</t>
+  </si>
+  <si>
+    <t>BGD17</t>
+  </si>
+  <si>
+    <t>BGD18</t>
+  </si>
+  <si>
+    <t>BGD19</t>
+  </si>
+  <si>
+    <t>BGD20</t>
+  </si>
+  <si>
+    <t>BGD21</t>
+  </si>
+  <si>
+    <t>BGD22</t>
+  </si>
+  <si>
+    <t>BGD23</t>
+  </si>
+  <si>
+    <t>BGD24</t>
+  </si>
+  <si>
+    <t>BGD25</t>
+  </si>
+  <si>
+    <t>BGD26</t>
+  </si>
+  <si>
+    <t>BGD28</t>
+  </si>
+  <si>
+    <t>BGD29</t>
+  </si>
+  <si>
+    <t>BGD30</t>
+  </si>
+  <si>
+    <t>BGD32</t>
+  </si>
+  <si>
+    <t>BGD33</t>
+  </si>
+  <si>
+    <t>BKHD01</t>
+  </si>
+  <si>
+    <t>BKHD02</t>
+  </si>
+  <si>
+    <t>BND01</t>
+  </si>
+  <si>
+    <t>BND03</t>
+  </si>
+  <si>
+    <t>BND04</t>
+  </si>
+  <si>
+    <t>BND05</t>
+  </si>
+  <si>
+    <t>BZD01</t>
+  </si>
+  <si>
+    <t>BZD02</t>
+  </si>
+  <si>
+    <t>BZD03</t>
+  </si>
+  <si>
+    <t>BZD04</t>
+  </si>
+  <si>
+    <t>BZD05</t>
+  </si>
+  <si>
+    <t>BZD06</t>
+  </si>
+  <si>
+    <t>BZD07</t>
+  </si>
+  <si>
+    <t>BZD08</t>
+  </si>
+  <si>
+    <t>BZD09</t>
+  </si>
+  <si>
+    <t>BZD10</t>
+  </si>
+  <si>
+    <t>BZD12</t>
+  </si>
+  <si>
+    <t>BZD13</t>
+  </si>
+  <si>
+    <t>BZD15</t>
+  </si>
+  <si>
+    <t>BZD16</t>
+  </si>
+  <si>
+    <t>BZD17</t>
+  </si>
+  <si>
+    <t>BZD18</t>
+  </si>
+  <si>
+    <t>BZD19</t>
+  </si>
+  <si>
+    <t>BZD20</t>
+  </si>
+  <si>
+    <t>BZD22</t>
+  </si>
+  <si>
+    <t>BZD23</t>
+  </si>
+  <si>
+    <t>BZD25</t>
+  </si>
+  <si>
+    <t>BZD26</t>
+  </si>
+  <si>
+    <t>BZD28</t>
+  </si>
+  <si>
+    <t>BZD30</t>
+  </si>
+  <si>
+    <t>BZD31</t>
+  </si>
+  <si>
+    <t>BZD32</t>
+  </si>
+  <si>
+    <t>BZD35</t>
+  </si>
+  <si>
+    <t>BZD36</t>
+  </si>
+  <si>
+    <t>BZD37</t>
+  </si>
+  <si>
+    <t>BZD38</t>
+  </si>
+  <si>
+    <t>BZD39</t>
+  </si>
+  <si>
+    <t>BZD40</t>
+  </si>
+  <si>
+    <t>BZD42</t>
+  </si>
+  <si>
+    <t>BZD43</t>
+  </si>
+  <si>
+    <t>CHD01</t>
+  </si>
+  <si>
+    <t>CHD02</t>
+  </si>
+  <si>
+    <t>CHD03</t>
+  </si>
+  <si>
+    <t>CHD04</t>
+  </si>
+  <si>
+    <t>CHD05</t>
+  </si>
+  <si>
+    <t>CHD06</t>
+  </si>
+  <si>
+    <t>CHD08</t>
+  </si>
+  <si>
+    <t>CHD09</t>
+  </si>
+  <si>
+    <t>CHD10</t>
+  </si>
+  <si>
+    <t>CHD11</t>
+  </si>
+  <si>
+    <t>CHD12</t>
+  </si>
+  <si>
+    <t>CHD13</t>
+  </si>
+  <si>
+    <t>CHD14</t>
+  </si>
+  <si>
+    <t>CHD15</t>
+  </si>
+  <si>
+    <t>CHD16</t>
+  </si>
+  <si>
+    <t>CHD17</t>
+  </si>
+  <si>
+    <t>CHD18</t>
+  </si>
+  <si>
+    <t>CHD19</t>
+  </si>
+  <si>
+    <t>CHD21</t>
+  </si>
+  <si>
+    <t>CHD23</t>
+  </si>
+  <si>
+    <t>DIS</t>
+  </si>
+  <si>
+    <t>ELD</t>
+  </si>
+  <si>
+    <t>KHUD01</t>
+  </si>
+  <si>
+    <t>KHUD02</t>
+  </si>
+  <si>
+    <t>KHUD03</t>
+  </si>
+  <si>
+    <t>KHUD05</t>
+  </si>
+  <si>
+    <t>KHUD06</t>
+  </si>
+  <si>
+    <t>KHUD07</t>
+  </si>
+  <si>
+    <t>KHUD08</t>
+  </si>
+  <si>
+    <t>KHUD09</t>
+  </si>
+  <si>
+    <t>KHUD10</t>
+  </si>
+  <si>
+    <t>KHUD11</t>
+  </si>
+  <si>
+    <t>KHUD12</t>
+  </si>
+  <si>
+    <t>KHUD13</t>
+  </si>
+  <si>
+    <t>KHUD14</t>
+  </si>
+  <si>
+    <t>KHUD15</t>
+  </si>
+  <si>
+    <t>KHUD17</t>
+  </si>
+  <si>
+    <t>KHUD18</t>
+  </si>
+  <si>
+    <t>KHUD19</t>
+  </si>
+  <si>
+    <t>KHUD20</t>
+  </si>
+  <si>
+    <t>KHUD21</t>
+  </si>
+  <si>
+    <t>KHUD22</t>
+  </si>
+  <si>
+    <t>KHUD23</t>
+  </si>
+  <si>
+    <t>KHUD24</t>
+  </si>
+  <si>
+    <t>KHUD25</t>
+  </si>
+  <si>
+    <t>ND01</t>
+  </si>
+  <si>
+    <t>ND02</t>
+  </si>
+  <si>
+    <t>ND03</t>
+  </si>
+  <si>
+    <t>ND04</t>
+  </si>
+  <si>
+    <t>ND05</t>
+  </si>
+  <si>
+    <t>ND06</t>
+  </si>
+  <si>
+    <t>ND07</t>
+  </si>
+  <si>
+    <t>ND08</t>
+  </si>
+  <si>
+    <t>SBD01</t>
+  </si>
+  <si>
+    <t>SBD02</t>
+  </si>
+  <si>
+    <t>SBD03</t>
+  </si>
+  <si>
+    <t>SBD04</t>
+  </si>
+  <si>
+    <t>SBD05</t>
+  </si>
+  <si>
+    <t>SBD06</t>
+  </si>
+  <si>
+    <t>SBD07</t>
+  </si>
+  <si>
+    <t>SBD08</t>
+  </si>
+  <si>
+    <t>SBD09</t>
+  </si>
+  <si>
+    <t>SBD10</t>
+  </si>
+  <si>
+    <t>SBD11</t>
+  </si>
+  <si>
+    <t>SBD12</t>
+  </si>
+  <si>
+    <t>SBD13</t>
+  </si>
+  <si>
+    <t>SBD14</t>
+  </si>
+  <si>
+    <t>SBD15</t>
+  </si>
+  <si>
+    <t>SBD16</t>
+  </si>
+  <si>
+    <t>SBD17</t>
+  </si>
+  <si>
+    <t>SBD18</t>
+  </si>
+  <si>
+    <t>SBD19</t>
+  </si>
+  <si>
+    <t>SBD20</t>
+  </si>
+  <si>
+    <t>SKHD01</t>
+  </si>
+  <si>
+    <t>SKHD02</t>
+  </si>
+  <si>
+    <t>SKHD03</t>
+  </si>
+  <si>
+    <t>SKHD04</t>
+  </si>
+  <si>
+    <t>SKHD05</t>
+  </si>
+  <si>
+    <t>SKHD06</t>
+  </si>
+  <si>
+    <t>SKHD07</t>
+  </si>
+  <si>
+    <t>SKHD08</t>
+  </si>
+  <si>
+    <t>SKHD09</t>
+  </si>
+  <si>
+    <t>SKHD11</t>
+  </si>
+  <si>
+    <t>SKHD12</t>
+  </si>
+  <si>
+    <t>SKHD13</t>
+  </si>
+  <si>
+    <t>SKHD14</t>
+  </si>
+  <si>
+    <t>SKHD15</t>
+  </si>
+  <si>
+    <t>SKHD16</t>
+  </si>
+  <si>
+    <t>SKHD17</t>
+  </si>
+  <si>
+    <t>SKHD18</t>
+  </si>
+  <si>
+    <t>SKHD19</t>
+  </si>
+  <si>
+    <t>SKHD20</t>
+  </si>
+  <si>
+    <t>SKHD21</t>
+  </si>
+  <si>
+    <t>SKHD22</t>
+  </si>
+  <si>
+    <t>SKHD23</t>
+  </si>
+  <si>
+    <t>SKHD24</t>
+  </si>
+  <si>
+    <t>SKHD25</t>
+  </si>
+  <si>
+    <t>SKHD26</t>
+  </si>
+  <si>
+    <t>SKHD27</t>
+  </si>
+  <si>
+    <t>SKHD28</t>
+  </si>
+  <si>
+    <t>SKHD29</t>
+  </si>
+  <si>
+    <t>SKHD30</t>
+  </si>
+  <si>
+    <t>SKHD31</t>
+  </si>
+  <si>
+    <t>SKHD32</t>
+  </si>
+  <si>
+    <t>SKHD33</t>
+  </si>
+  <si>
+    <t>SKHD34</t>
+  </si>
+  <si>
+    <t>SKHD35</t>
+  </si>
+  <si>
+    <t>SKHD36</t>
+  </si>
+  <si>
+    <t>SKHD37</t>
+  </si>
+  <si>
+    <t>SKHD38</t>
+  </si>
+  <si>
+    <t>SKHD39</t>
+  </si>
+  <si>
+    <t>SKHD40</t>
+  </si>
+  <si>
+    <t>SKHD41</t>
+  </si>
+  <si>
+    <t>SKHD42</t>
+  </si>
+  <si>
+    <t>SKHD43</t>
+  </si>
+  <si>
+    <t>STU</t>
+  </si>
+  <si>
+    <t>WOM</t>
+  </si>
+  <si>
+    <t>YTH</t>
+  </si>
+  <si>
+    <t>BGD01.xlsx</t>
+  </si>
+  <si>
+    <t>BGD02.xlsx</t>
+  </si>
+  <si>
+    <t>BGD04.xlsx</t>
+  </si>
+  <si>
+    <t>BGD05.xlsx</t>
+  </si>
+  <si>
+    <t>BGD06.xlsx</t>
+  </si>
+  <si>
+    <t>BGD08.xlsx</t>
+  </si>
+  <si>
+    <t>BGD09.xlsx</t>
+  </si>
+  <si>
+    <t>BGD10.xlsx</t>
+  </si>
+  <si>
+    <t>BGD11.xlsx</t>
+  </si>
+  <si>
+    <t>BGD12.xlsx</t>
+  </si>
+  <si>
+    <t>BGD15.xlsx</t>
+  </si>
+  <si>
+    <t>BGD16.xlsx</t>
+  </si>
+  <si>
+    <t>BGD17.xlsx</t>
+  </si>
+  <si>
+    <t>BGD18.xlsx</t>
+  </si>
+  <si>
+    <t>BGD19.xlsx</t>
+  </si>
+  <si>
+    <t>BGD20.xlsx</t>
+  </si>
+  <si>
+    <t>BGD21.xlsx</t>
+  </si>
+  <si>
+    <t>BGD22.xlsx</t>
+  </si>
+  <si>
+    <t>BGD23.xlsx</t>
+  </si>
+  <si>
+    <t>BGD24.xlsx</t>
+  </si>
+  <si>
+    <t>BGD25.xlsx</t>
+  </si>
+  <si>
+    <t>BGD26.xlsx</t>
+  </si>
+  <si>
+    <t>BGD28.xlsx</t>
+  </si>
+  <si>
+    <t>BGD29.xlsx</t>
+  </si>
+  <si>
+    <t>BGD30.xlsx</t>
+  </si>
+  <si>
+    <t>BGD32.xlsx</t>
+  </si>
+  <si>
+    <t>BGD33.xlsx</t>
+  </si>
+  <si>
+    <t>BKHD01.xlsx</t>
+  </si>
+  <si>
+    <t>BKHD02.xlsx</t>
+  </si>
+  <si>
+    <t>BND01.xlsx</t>
+  </si>
+  <si>
+    <t>BND03.xlsx</t>
+  </si>
+  <si>
+    <t>BND04.xlsx</t>
+  </si>
+  <si>
+    <t>BND05.xlsx</t>
+  </si>
+  <si>
+    <t>BZD01.xlsx</t>
+  </si>
+  <si>
+    <t>BZD02.xlsx</t>
+  </si>
+  <si>
+    <t>BZD03.xlsx</t>
+  </si>
+  <si>
+    <t>BZD04.xlsx</t>
+  </si>
+  <si>
+    <t>BZD05.xlsx</t>
+  </si>
+  <si>
+    <t>BZD06.xlsx</t>
+  </si>
+  <si>
+    <t>BZD07.xlsx</t>
+  </si>
+  <si>
+    <t>BZD08.xlsx</t>
+  </si>
+  <si>
+    <t>BZD09.xlsx</t>
+  </si>
+  <si>
+    <t>BZD10.xlsx</t>
+  </si>
+  <si>
+    <t>BZD12.xlsx</t>
+  </si>
+  <si>
+    <t>BZD13.xlsx</t>
+  </si>
+  <si>
+    <t>BZD15.xlsx</t>
+  </si>
+  <si>
+    <t>BZD16.xlsx</t>
+  </si>
+  <si>
+    <t>BZD17.xlsx</t>
+  </si>
+  <si>
+    <t>BZD18.xlsx</t>
+  </si>
+  <si>
+    <t>BZD19.xlsx</t>
+  </si>
+  <si>
+    <t>BZD20.xlsx</t>
+  </si>
+  <si>
+    <t>BZD22.xlsx</t>
+  </si>
+  <si>
+    <t>BZD23.xlsx</t>
+  </si>
+  <si>
+    <t>BZD25.xlsx</t>
+  </si>
+  <si>
+    <t>BZD26.xlsx</t>
+  </si>
+  <si>
+    <t>BZD28.xlsx</t>
+  </si>
+  <si>
+    <t>BZD30.xlsx</t>
+  </si>
+  <si>
+    <t>BZD31.xlsx</t>
+  </si>
+  <si>
+    <t>BZD32.xlsx</t>
+  </si>
+  <si>
+    <t>BZD35.xlsx</t>
+  </si>
+  <si>
+    <t>BZD36.xlsx</t>
+  </si>
+  <si>
+    <t>BZD37.xlsx</t>
+  </si>
+  <si>
+    <t>BZD38.xlsx</t>
+  </si>
+  <si>
+    <t>BZD39.xlsx</t>
+  </si>
+  <si>
+    <t>BZD40.xlsx</t>
+  </si>
+  <si>
+    <t>BZD42.xlsx</t>
+  </si>
+  <si>
+    <t>BZD43.xlsx</t>
+  </si>
+  <si>
+    <t>CHD01.xlsx</t>
+  </si>
+  <si>
+    <t>CHD02.xlsx</t>
+  </si>
+  <si>
+    <t>CHD03.xlsx</t>
+  </si>
+  <si>
+    <t>CHD04.xlsx</t>
+  </si>
+  <si>
+    <t>CHD05.xlsx</t>
+  </si>
+  <si>
+    <t>CHD06.xlsx</t>
+  </si>
+  <si>
+    <t>CHD08.xlsx</t>
+  </si>
+  <si>
+    <t>CHD09.xlsx</t>
+  </si>
+  <si>
+    <t>CHD10.xlsx</t>
+  </si>
+  <si>
+    <t>CHD11.xlsx</t>
+  </si>
+  <si>
+    <t>CHD12.xlsx</t>
+  </si>
+  <si>
+    <t>CHD13.xlsx</t>
+  </si>
+  <si>
+    <t>CHD14.xlsx</t>
+  </si>
+  <si>
+    <t>CHD15.xlsx</t>
+  </si>
+  <si>
+    <t>CHD16.xlsx</t>
+  </si>
+  <si>
+    <t>CHD17.xlsx</t>
+  </si>
+  <si>
+    <t>CHD18.xlsx</t>
+  </si>
+  <si>
+    <t>CHD19.xlsx</t>
+  </si>
+  <si>
+    <t>CHD21.xlsx</t>
+  </si>
+  <si>
+    <t>CHD23.xlsx</t>
+  </si>
+  <si>
+    <t>DIS.xlsx</t>
+  </si>
+  <si>
+    <t>ELD.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD01.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD02.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD03.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD05.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD06.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD07.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD08.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD09.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD10.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD11.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD12.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD13.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD14.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD15.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD17.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD18.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD19.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD20.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD21.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD22.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD23.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD24.xlsx</t>
+  </si>
+  <si>
+    <t>KHUD25.xlsx</t>
+  </si>
+  <si>
+    <t>ND01.xlsx</t>
+  </si>
+  <si>
+    <t>ND02.xlsx</t>
+  </si>
+  <si>
+    <t>ND03.xlsx</t>
+  </si>
+  <si>
+    <t>ND04.xlsx</t>
+  </si>
+  <si>
+    <t>ND05.xlsx</t>
+  </si>
+  <si>
+    <t>ND06.xlsx</t>
+  </si>
+  <si>
+    <t>ND07.xlsx</t>
+  </si>
+  <si>
+    <t>ND08.xlsx</t>
+  </si>
+  <si>
+    <t>SBD01.xlsx</t>
+  </si>
+  <si>
+    <t>SBD02.xlsx</t>
+  </si>
+  <si>
+    <t>SBD03.xlsx</t>
+  </si>
+  <si>
+    <t>SBD04.xlsx</t>
+  </si>
+  <si>
+    <t>SBD05.xlsx</t>
+  </si>
+  <si>
+    <t>SBD06.xlsx</t>
+  </si>
+  <si>
+    <t>SBD07.xlsx</t>
+  </si>
+  <si>
+    <t>SBD08.xlsx</t>
+  </si>
+  <si>
+    <t>SBD09.xlsx</t>
+  </si>
+  <si>
+    <t>SBD10.xlsx</t>
+  </si>
+  <si>
+    <t>SBD11.xlsx</t>
+  </si>
+  <si>
+    <t>SBD12.xlsx</t>
+  </si>
+  <si>
+    <t>SBD13.xlsx</t>
+  </si>
+  <si>
+    <t>SBD14.xlsx</t>
+  </si>
+  <si>
+    <t>SBD15.xlsx</t>
+  </si>
+  <si>
+    <t>SBD16.xlsx</t>
+  </si>
+  <si>
+    <t>SBD17.xlsx</t>
+  </si>
+  <si>
+    <t>SBD18.xlsx</t>
+  </si>
+  <si>
+    <t>SBD19.xlsx</t>
+  </si>
+  <si>
+    <t>SBD20.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD01.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD02.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD03.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD04.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD05.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD06.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD07.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD08.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD09.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD11.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD12.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD13.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD14.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD15.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD16.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD17.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD18.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD19.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD20.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD21.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD22.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD23.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD24.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD25.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD26.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD27.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD28.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD29.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD30.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD31.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD32.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD33.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD34.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD35.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD36.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD37.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD38.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD39.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD40.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD41.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD42.xlsx</t>
+  </si>
+  <si>
+    <t>SKHD43.xlsx</t>
+  </si>
+  <si>
+    <t>STU.xlsx</t>
+  </si>
+  <si>
+    <t>WOM.xlsx</t>
+  </si>
+  <si>
+    <t>YTH.xlsx</t>
   </si>
 </sst>
 </file>
@@ -438,82 +1535,2616 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="10.9375" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:D186"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.6875" customWidth="1"/>
-    <col min="2" max="2" width="12.9375" customWidth="1"/>
-    <col min="4" max="4" width="12.875" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>0</v>
-      </c>
       <c r="D2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>190</v>
       </c>
       <c r="C3" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>191</v>
       </c>
       <c r="C4" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>194</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C8" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
+      <c r="D8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>197</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>199</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>200</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>201</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>202</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>204</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>205</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>206</v>
+      </c>
+      <c r="C19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>207</v>
+      </c>
+      <c r="C20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>208</v>
+      </c>
+      <c r="C21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>209</v>
+      </c>
+      <c r="C22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>210</v>
+      </c>
+      <c r="C23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>211</v>
+      </c>
+      <c r="C24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>212</v>
+      </c>
+      <c r="C25" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>213</v>
+      </c>
+      <c r="C26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>214</v>
+      </c>
+      <c r="C27" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>215</v>
+      </c>
+      <c r="C28" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>216</v>
+      </c>
+      <c r="C29" t="s">
+        <v>31</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>217</v>
+      </c>
+      <c r="C30" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>218</v>
+      </c>
+      <c r="C31" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>219</v>
+      </c>
+      <c r="C32" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>220</v>
+      </c>
+      <c r="C33" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>221</v>
+      </c>
+      <c r="C34" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>222</v>
+      </c>
+      <c r="C35" t="s">
+        <v>37</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>223</v>
+      </c>
+      <c r="C36" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>224</v>
+      </c>
+      <c r="C37" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>225</v>
+      </c>
+      <c r="C38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>226</v>
+      </c>
+      <c r="C39" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>227</v>
+      </c>
+      <c r="C40" t="s">
+        <v>42</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>228</v>
+      </c>
+      <c r="C41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>229</v>
+      </c>
+      <c r="C42" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>230</v>
+      </c>
+      <c r="C43" t="s">
+        <v>45</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>231</v>
+      </c>
+      <c r="C44" t="s">
+        <v>46</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>232</v>
+      </c>
+      <c r="C45" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>233</v>
+      </c>
+      <c r="C46" t="s">
+        <v>48</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>234</v>
+      </c>
+      <c r="C47" t="s">
+        <v>49</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>235</v>
+      </c>
+      <c r="C48" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>236</v>
+      </c>
+      <c r="C49" t="s">
+        <v>51</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>237</v>
+      </c>
+      <c r="C50" t="s">
+        <v>52</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>238</v>
+      </c>
+      <c r="C51" t="s">
+        <v>53</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>239</v>
+      </c>
+      <c r="C52" t="s">
+        <v>54</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>240</v>
+      </c>
+      <c r="C53" t="s">
+        <v>55</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>241</v>
+      </c>
+      <c r="C54" t="s">
+        <v>56</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>242</v>
+      </c>
+      <c r="C55" t="s">
+        <v>57</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>243</v>
+      </c>
+      <c r="C56" t="s">
+        <v>58</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>244</v>
+      </c>
+      <c r="C57" t="s">
+        <v>59</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>245</v>
+      </c>
+      <c r="C58" t="s">
+        <v>60</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>246</v>
+      </c>
+      <c r="C59" t="s">
+        <v>61</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>247</v>
+      </c>
+      <c r="C60" t="s">
+        <v>62</v>
+      </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>248</v>
+      </c>
+      <c r="C61" t="s">
+        <v>63</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>249</v>
+      </c>
+      <c r="C62" t="s">
+        <v>64</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>250</v>
+      </c>
+      <c r="C63" t="s">
+        <v>65</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>251</v>
+      </c>
+      <c r="C64" t="s">
+        <v>66</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>252</v>
+      </c>
+      <c r="C65" t="s">
+        <v>67</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>253</v>
+      </c>
+      <c r="C66" t="s">
+        <v>68</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>254</v>
+      </c>
+      <c r="C67" t="s">
+        <v>69</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>255</v>
+      </c>
+      <c r="C68" t="s">
+        <v>70</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>256</v>
+      </c>
+      <c r="C69" t="s">
+        <v>71</v>
+      </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>257</v>
+      </c>
+      <c r="C70" t="s">
+        <v>72</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>258</v>
+      </c>
+      <c r="C71" t="s">
+        <v>73</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>259</v>
+      </c>
+      <c r="C72" t="s">
+        <v>74</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>260</v>
+      </c>
+      <c r="C73" t="s">
+        <v>75</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>261</v>
+      </c>
+      <c r="C74" t="s">
+        <v>76</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>262</v>
+      </c>
+      <c r="C75" t="s">
+        <v>77</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>263</v>
+      </c>
+      <c r="C76" t="s">
+        <v>78</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>264</v>
+      </c>
+      <c r="C77" t="s">
+        <v>79</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>265</v>
+      </c>
+      <c r="C78" t="s">
+        <v>80</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>266</v>
+      </c>
+      <c r="C79" t="s">
+        <v>81</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>267</v>
+      </c>
+      <c r="C80" t="s">
+        <v>82</v>
+      </c>
+      <c r="D80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>268</v>
+      </c>
+      <c r="C81" t="s">
+        <v>83</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>269</v>
+      </c>
+      <c r="C82" t="s">
+        <v>84</v>
+      </c>
+      <c r="D82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>270</v>
+      </c>
+      <c r="C83" t="s">
+        <v>85</v>
+      </c>
+      <c r="D83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>271</v>
+      </c>
+      <c r="C84" t="s">
+        <v>86</v>
+      </c>
+      <c r="D84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>272</v>
+      </c>
+      <c r="C85" t="s">
+        <v>87</v>
+      </c>
+      <c r="D85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>273</v>
+      </c>
+      <c r="C86" t="s">
+        <v>88</v>
+      </c>
+      <c r="D86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>274</v>
+      </c>
+      <c r="C87" t="s">
+        <v>89</v>
+      </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>275</v>
+      </c>
+      <c r="C88" t="s">
+        <v>90</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>276</v>
+      </c>
+      <c r="C89" t="s">
+        <v>91</v>
+      </c>
+      <c r="D89">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>277</v>
+      </c>
+      <c r="C90" t="s">
+        <v>92</v>
+      </c>
+      <c r="D90">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>278</v>
+      </c>
+      <c r="C91" t="s">
+        <v>93</v>
+      </c>
+      <c r="D91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>279</v>
+      </c>
+      <c r="C92" t="s">
+        <v>94</v>
+      </c>
+      <c r="D92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>280</v>
+      </c>
+      <c r="C93" t="s">
+        <v>95</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>281</v>
+      </c>
+      <c r="C94" t="s">
+        <v>96</v>
+      </c>
+      <c r="D94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>282</v>
+      </c>
+      <c r="C95" t="s">
+        <v>97</v>
+      </c>
+      <c r="D95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>283</v>
+      </c>
+      <c r="C96" t="s">
+        <v>98</v>
+      </c>
+      <c r="D96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>284</v>
+      </c>
+      <c r="C97" t="s">
+        <v>99</v>
+      </c>
+      <c r="D97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>285</v>
+      </c>
+      <c r="C98" t="s">
+        <v>100</v>
+      </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>286</v>
+      </c>
+      <c r="C99" t="s">
+        <v>101</v>
+      </c>
+      <c r="D99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>287</v>
+      </c>
+      <c r="C100" t="s">
+        <v>102</v>
+      </c>
+      <c r="D100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>288</v>
+      </c>
+      <c r="C101" t="s">
+        <v>103</v>
+      </c>
+      <c r="D101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>289</v>
+      </c>
+      <c r="C102" t="s">
+        <v>104</v>
+      </c>
+      <c r="D102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>290</v>
+      </c>
+      <c r="C103" t="s">
+        <v>105</v>
+      </c>
+      <c r="D103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>291</v>
+      </c>
+      <c r="C104" t="s">
+        <v>106</v>
+      </c>
+      <c r="D104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>292</v>
+      </c>
+      <c r="C105" t="s">
+        <v>107</v>
+      </c>
+      <c r="D105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>293</v>
+      </c>
+      <c r="C106" t="s">
+        <v>108</v>
+      </c>
+      <c r="D106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>294</v>
+      </c>
+      <c r="C107" t="s">
+        <v>109</v>
+      </c>
+      <c r="D107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>295</v>
+      </c>
+      <c r="C108" t="s">
+        <v>110</v>
+      </c>
+      <c r="D108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>296</v>
+      </c>
+      <c r="C109" t="s">
+        <v>111</v>
+      </c>
+      <c r="D109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>297</v>
+      </c>
+      <c r="C110" t="s">
+        <v>112</v>
+      </c>
+      <c r="D110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>298</v>
+      </c>
+      <c r="C111" t="s">
+        <v>113</v>
+      </c>
+      <c r="D111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>299</v>
+      </c>
+      <c r="C112" t="s">
+        <v>114</v>
+      </c>
+      <c r="D112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>300</v>
+      </c>
+      <c r="C113" t="s">
+        <v>115</v>
+      </c>
+      <c r="D113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>301</v>
+      </c>
+      <c r="C114" t="s">
+        <v>116</v>
+      </c>
+      <c r="D114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>302</v>
+      </c>
+      <c r="C115" t="s">
+        <v>117</v>
+      </c>
+      <c r="D115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>303</v>
+      </c>
+      <c r="C116" t="s">
+        <v>118</v>
+      </c>
+      <c r="D116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>304</v>
+      </c>
+      <c r="C117" t="s">
+        <v>119</v>
+      </c>
+      <c r="D117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>305</v>
+      </c>
+      <c r="C118" t="s">
+        <v>120</v>
+      </c>
+      <c r="D118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>306</v>
+      </c>
+      <c r="C119" t="s">
+        <v>121</v>
+      </c>
+      <c r="D119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>307</v>
+      </c>
+      <c r="C120" t="s">
+        <v>122</v>
+      </c>
+      <c r="D120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>308</v>
+      </c>
+      <c r="C121" t="s">
+        <v>123</v>
+      </c>
+      <c r="D121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>309</v>
+      </c>
+      <c r="C122" t="s">
+        <v>124</v>
+      </c>
+      <c r="D122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
+        <v>310</v>
+      </c>
+      <c r="C123" t="s">
+        <v>125</v>
+      </c>
+      <c r="D123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>311</v>
+      </c>
+      <c r="C124" t="s">
+        <v>126</v>
+      </c>
+      <c r="D124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>312</v>
+      </c>
+      <c r="C125" t="s">
+        <v>127</v>
+      </c>
+      <c r="D125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
+        <v>313</v>
+      </c>
+      <c r="C126" t="s">
+        <v>128</v>
+      </c>
+      <c r="D126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>314</v>
+      </c>
+      <c r="C127" t="s">
+        <v>129</v>
+      </c>
+      <c r="D127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>315</v>
+      </c>
+      <c r="C128" t="s">
+        <v>130</v>
+      </c>
+      <c r="D128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>316</v>
+      </c>
+      <c r="C129" t="s">
+        <v>131</v>
+      </c>
+      <c r="D129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>317</v>
+      </c>
+      <c r="C130" t="s">
+        <v>132</v>
+      </c>
+      <c r="D130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>318</v>
+      </c>
+      <c r="C131" t="s">
+        <v>133</v>
+      </c>
+      <c r="D131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>319</v>
+      </c>
+      <c r="C132" t="s">
+        <v>134</v>
+      </c>
+      <c r="D132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>320</v>
+      </c>
+      <c r="C133" t="s">
+        <v>135</v>
+      </c>
+      <c r="D133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>321</v>
+      </c>
+      <c r="C134" t="s">
+        <v>136</v>
+      </c>
+      <c r="D134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>322</v>
+      </c>
+      <c r="C135" t="s">
+        <v>137</v>
+      </c>
+      <c r="D135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>323</v>
+      </c>
+      <c r="C136" t="s">
+        <v>138</v>
+      </c>
+      <c r="D136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>324</v>
+      </c>
+      <c r="C137" t="s">
+        <v>139</v>
+      </c>
+      <c r="D137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>325</v>
+      </c>
+      <c r="C138" t="s">
+        <v>140</v>
+      </c>
+      <c r="D138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>326</v>
+      </c>
+      <c r="C139" t="s">
+        <v>141</v>
+      </c>
+      <c r="D139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>327</v>
+      </c>
+      <c r="C140" t="s">
+        <v>142</v>
+      </c>
+      <c r="D140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>328</v>
+      </c>
+      <c r="C141" t="s">
+        <v>143</v>
+      </c>
+      <c r="D141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>329</v>
+      </c>
+      <c r="C142" t="s">
+        <v>144</v>
+      </c>
+      <c r="D142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>330</v>
+      </c>
+      <c r="C143" t="s">
+        <v>145</v>
+      </c>
+      <c r="D143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>331</v>
+      </c>
+      <c r="C144" t="s">
+        <v>146</v>
+      </c>
+      <c r="D144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>332</v>
+      </c>
+      <c r="C145" t="s">
+        <v>147</v>
+      </c>
+      <c r="D145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>333</v>
+      </c>
+      <c r="C146" t="s">
+        <v>148</v>
+      </c>
+      <c r="D146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>334</v>
+      </c>
+      <c r="C147" t="s">
+        <v>149</v>
+      </c>
+      <c r="D147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>335</v>
+      </c>
+      <c r="C148" t="s">
+        <v>150</v>
+      </c>
+      <c r="D148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>336</v>
+      </c>
+      <c r="C149" t="s">
+        <v>151</v>
+      </c>
+      <c r="D149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>337</v>
+      </c>
+      <c r="C150" t="s">
+        <v>152</v>
+      </c>
+      <c r="D150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>338</v>
+      </c>
+      <c r="C151" t="s">
+        <v>153</v>
+      </c>
+      <c r="D151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>339</v>
+      </c>
+      <c r="C152" t="s">
+        <v>154</v>
+      </c>
+      <c r="D152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
+        <v>340</v>
+      </c>
+      <c r="C153" t="s">
+        <v>155</v>
+      </c>
+      <c r="D153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
+        <v>341</v>
+      </c>
+      <c r="C154" t="s">
+        <v>156</v>
+      </c>
+      <c r="D154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
+        <v>342</v>
+      </c>
+      <c r="C155" t="s">
+        <v>157</v>
+      </c>
+      <c r="D155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156" t="s">
+        <v>343</v>
+      </c>
+      <c r="C156" t="s">
+        <v>158</v>
+      </c>
+      <c r="D156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157" t="s">
+        <v>344</v>
+      </c>
+      <c r="C157" t="s">
+        <v>159</v>
+      </c>
+      <c r="D157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158" t="s">
+        <v>345</v>
+      </c>
+      <c r="C158" t="s">
+        <v>160</v>
+      </c>
+      <c r="D158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159" t="s">
+        <v>346</v>
+      </c>
+      <c r="C159" t="s">
+        <v>161</v>
+      </c>
+      <c r="D159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160" t="s">
+        <v>347</v>
+      </c>
+      <c r="C160" t="s">
+        <v>162</v>
+      </c>
+      <c r="D160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161" t="s">
+        <v>348</v>
+      </c>
+      <c r="C161" t="s">
+        <v>163</v>
+      </c>
+      <c r="D161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162" t="s">
+        <v>349</v>
+      </c>
+      <c r="C162" t="s">
+        <v>164</v>
+      </c>
+      <c r="D162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163" t="s">
+        <v>350</v>
+      </c>
+      <c r="C163" t="s">
+        <v>165</v>
+      </c>
+      <c r="D163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164" t="s">
+        <v>351</v>
+      </c>
+      <c r="C164" t="s">
+        <v>166</v>
+      </c>
+      <c r="D164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165" t="s">
+        <v>352</v>
+      </c>
+      <c r="C165" t="s">
+        <v>167</v>
+      </c>
+      <c r="D165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166" t="s">
+        <v>353</v>
+      </c>
+      <c r="C166" t="s">
+        <v>168</v>
+      </c>
+      <c r="D166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167" t="s">
+        <v>354</v>
+      </c>
+      <c r="C167" t="s">
+        <v>169</v>
+      </c>
+      <c r="D167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168" t="s">
+        <v>355</v>
+      </c>
+      <c r="C168" t="s">
+        <v>170</v>
+      </c>
+      <c r="D168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169" t="s">
+        <v>356</v>
+      </c>
+      <c r="C169" t="s">
+        <v>171</v>
+      </c>
+      <c r="D169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170" t="s">
+        <v>357</v>
+      </c>
+      <c r="C170" t="s">
+        <v>172</v>
+      </c>
+      <c r="D170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171" t="s">
+        <v>358</v>
+      </c>
+      <c r="C171" t="s">
+        <v>173</v>
+      </c>
+      <c r="D171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172" t="s">
+        <v>359</v>
+      </c>
+      <c r="C172" t="s">
+        <v>174</v>
+      </c>
+      <c r="D172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173" t="s">
+        <v>360</v>
+      </c>
+      <c r="C173" t="s">
+        <v>175</v>
+      </c>
+      <c r="D173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174" t="s">
+        <v>361</v>
+      </c>
+      <c r="C174" t="s">
+        <v>176</v>
+      </c>
+      <c r="D174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175" t="s">
+        <v>362</v>
+      </c>
+      <c r="C175" t="s">
+        <v>177</v>
+      </c>
+      <c r="D175">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176" t="s">
+        <v>363</v>
+      </c>
+      <c r="C176" t="s">
+        <v>178</v>
+      </c>
+      <c r="D176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177" t="s">
+        <v>364</v>
+      </c>
+      <c r="C177" t="s">
+        <v>179</v>
+      </c>
+      <c r="D177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A178">
+        <v>177</v>
+      </c>
+      <c r="B178" t="s">
+        <v>365</v>
+      </c>
+      <c r="C178" t="s">
+        <v>180</v>
+      </c>
+      <c r="D178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A179">
+        <v>178</v>
+      </c>
+      <c r="B179" t="s">
+        <v>366</v>
+      </c>
+      <c r="C179" t="s">
+        <v>181</v>
+      </c>
+      <c r="D179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A180">
+        <v>179</v>
+      </c>
+      <c r="B180" t="s">
+        <v>367</v>
+      </c>
+      <c r="C180" t="s">
+        <v>182</v>
+      </c>
+      <c r="D180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A181">
+        <v>180</v>
+      </c>
+      <c r="B181" t="s">
+        <v>368</v>
+      </c>
+      <c r="C181" t="s">
+        <v>183</v>
+      </c>
+      <c r="D181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A182">
+        <v>181</v>
+      </c>
+      <c r="B182" t="s">
+        <v>369</v>
+      </c>
+      <c r="C182" t="s">
+        <v>184</v>
+      </c>
+      <c r="D182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A183">
+        <v>182</v>
+      </c>
+      <c r="B183" t="s">
+        <v>370</v>
+      </c>
+      <c r="C183" t="s">
+        <v>185</v>
+      </c>
+      <c r="D183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A184">
+        <v>183</v>
+      </c>
+      <c r="B184" t="s">
+        <v>371</v>
+      </c>
+      <c r="C184" t="s">
+        <v>186</v>
+      </c>
+      <c r="D184">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A185">
+        <v>184</v>
+      </c>
+      <c r="B185" t="s">
+        <v>372</v>
+      </c>
+      <c r="C185" t="s">
+        <v>187</v>
+      </c>
+      <c r="D185">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A186">
+        <v>185</v>
+      </c>
+      <c r="B186" t="s">
+        <v>373</v>
+      </c>
+      <c r="C186" t="s">
+        <v>188</v>
+      </c>
+      <c r="D186">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
